--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16026EC7-BEA1-4C34-91DB-6A527A0C5B96}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1154489-412D-486A-A6F1-9406BCA22510}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
   <si>
     <t>Dato</t>
   </si>
@@ -79,6 +79,120 @@
   </si>
   <si>
     <t>Snakket litt om fadderuka</t>
+  </si>
+  <si>
+    <t>12:25-12:55</t>
+  </si>
+  <si>
+    <t>Laget Github repository</t>
+  </si>
+  <si>
+    <t>Gikk på do</t>
+  </si>
+  <si>
+    <t>2 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>3 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Snakket om fadderuka</t>
+  </si>
+  <si>
+    <t>13:00-1325</t>
+  </si>
+  <si>
+    <t>Så på telefon</t>
+  </si>
+  <si>
+    <t>Skrev om mål/delmål</t>
+  </si>
+  <si>
+    <t>Begynte å se på Wokwi</t>
+  </si>
+  <si>
+    <t>Prøver og fortså github bedre</t>
+  </si>
+  <si>
+    <t>13:00-13.25</t>
+  </si>
+  <si>
+    <t>Førte inn dette</t>
+  </si>
+  <si>
+    <t>Drakk kaffe</t>
+  </si>
+  <si>
+    <t>13:25-1400</t>
+  </si>
+  <si>
+    <t>4 (25 min + 10 min)</t>
+  </si>
+  <si>
+    <t>Skrev videre på mål og delmål</t>
+  </si>
+  <si>
+    <t>Gikk ut en tur for luft. Snakket med medstudenter.</t>
+  </si>
+  <si>
+    <t>Gikk på do, og var ute i finværet</t>
+  </si>
+  <si>
+    <t>Hadde problemer med syncing av OneDrive så prøvde å fikse det</t>
+  </si>
+  <si>
+    <t>1400-1435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (25 min +5 min) </t>
+  </si>
+  <si>
+    <t>Gikk på do, spilte bordfotball</t>
+  </si>
+  <si>
+    <t>3(25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>14:35-1500</t>
+  </si>
+  <si>
+    <t>6 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ble ferdig med mål og delmål</t>
+  </si>
+  <si>
+    <t>Snakket om quiz på samfunnet</t>
+  </si>
+  <si>
+    <t>Snakket om Quizlaget til Håkon</t>
+  </si>
+  <si>
+    <t>15:00-15:30</t>
+  </si>
+  <si>
+    <t>7 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ferdig med begrensninger og satt inn bilder</t>
+  </si>
+  <si>
+    <t>Jobbet med skisse påWokwi</t>
+  </si>
+  <si>
+    <t>15:40-16:05</t>
+  </si>
+  <si>
+    <t>8 (25 min) ferdig</t>
+  </si>
+  <si>
+    <t>Ble ferdig med disposisjon</t>
+  </si>
+  <si>
+    <t>Lagt inn Wokwi-skisse i dsposisjon og skrevet komponentliste</t>
+  </si>
+  <si>
+    <t>Ferdig</t>
   </si>
 </sst>
 </file>
@@ -114,9 +228,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,6 +250,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -451,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -460,7 +582,7 @@
     <col min="5" max="5" width="26.77734375" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" customWidth="1"/>
-    <col min="8" max="8" width="27.77734375" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" customWidth="1"/>
     <col min="9" max="9" width="25.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
   </cols>
@@ -526,6 +648,185 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -533,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -541,7 +842,8 @@
     <col min="5" max="5" width="14.21875" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -587,6 +889,206 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1154489-412D-486A-A6F1-9406BCA22510}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8CA1487-953B-461D-8CAA-82A04A7FA363}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
     <sheet name="Brage" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
   <si>
     <t>Dato</t>
   </si>
@@ -60,6 +60,9 @@
     <t>Tretthet (1–10)</t>
   </si>
   <si>
+    <t>Fremgang</t>
+  </si>
+  <si>
     <t>Pausens innhold</t>
   </si>
   <si>
@@ -72,9 +75,6 @@
     <t>1 (25 min + 5 min)</t>
   </si>
   <si>
-    <t>Fremgang</t>
-  </si>
-  <si>
     <t>Gjorde ferdig problemstilling.</t>
   </si>
   <si>
@@ -84,115 +84,151 @@
     <t>12:25-12:55</t>
   </si>
   <si>
+    <t>2 (25 min + 5 min)</t>
+  </si>
+  <si>
     <t>Laget Github repository</t>
   </si>
   <si>
     <t>Gikk på do</t>
   </si>
   <si>
-    <t>2 (25 min + 5 min)</t>
+    <t>13:00-1325</t>
   </si>
   <si>
     <t>3 (25 min + 5 min)</t>
   </si>
   <si>
+    <t>Prøver og fortså github bedre</t>
+  </si>
+  <si>
+    <t>Drakk kaffe</t>
+  </si>
+  <si>
+    <t>13:25-1400</t>
+  </si>
+  <si>
+    <t>4 (25 min + 10 min)</t>
+  </si>
+  <si>
+    <t>Skrev videre på mål og delmål</t>
+  </si>
+  <si>
+    <t>Gikk ut en tur for luft. Snakket med medstudenter.</t>
+  </si>
+  <si>
+    <t>1400-1435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (25 min +5 min) </t>
+  </si>
+  <si>
+    <t>Gikk på do, spilte bordfotball</t>
+  </si>
+  <si>
+    <t>14:35-1500</t>
+  </si>
+  <si>
+    <t>6 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ble ferdig med mål og delmål</t>
+  </si>
+  <si>
+    <t>Snakket om quiz på samfunnet</t>
+  </si>
+  <si>
+    <t>15:00-15:30</t>
+  </si>
+  <si>
+    <t>7 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ferdig med begrensninger og satt inn bilder</t>
+  </si>
+  <si>
+    <t>15:40-16:05</t>
+  </si>
+  <si>
+    <t>8 (25 min) ferdig</t>
+  </si>
+  <si>
+    <t>Ble ferdig med disposisjon</t>
+  </si>
+  <si>
+    <t>Skrev om mål/delmål</t>
+  </si>
+  <si>
     <t>Snakket om fadderuka</t>
   </si>
   <si>
-    <t>13:00-1325</t>
-  </si>
-  <si>
     <t>Så på telefon</t>
   </si>
   <si>
-    <t>Skrev om mål/delmål</t>
+    <t>13:00-13.25</t>
+  </si>
+  <si>
+    <t>3(25 min + 5 min)</t>
   </si>
   <si>
     <t>Begynte å se på Wokwi</t>
   </si>
   <si>
-    <t>Prøver og fortså github bedre</t>
-  </si>
-  <si>
-    <t>13:00-13.25</t>
-  </si>
-  <si>
     <t>Førte inn dette</t>
   </si>
   <si>
-    <t>Drakk kaffe</t>
-  </si>
-  <si>
-    <t>13:25-1400</t>
-  </si>
-  <si>
-    <t>4 (25 min + 10 min)</t>
-  </si>
-  <si>
-    <t>Skrev videre på mål og delmål</t>
-  </si>
-  <si>
-    <t>Gikk ut en tur for luft. Snakket med medstudenter.</t>
+    <t>Hadde problemer med syncing av OneDrive så prøvde å fikse det</t>
   </si>
   <si>
     <t>Gikk på do, og var ute i finværet</t>
   </si>
   <si>
-    <t>Hadde problemer med syncing av OneDrive så prøvde å fikse det</t>
-  </si>
-  <si>
-    <t>1400-1435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (25 min +5 min) </t>
-  </si>
-  <si>
-    <t>Gikk på do, spilte bordfotball</t>
-  </si>
-  <si>
-    <t>3(25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>14:35-1500</t>
-  </si>
-  <si>
-    <t>6 (25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Ble ferdig med mål og delmål</t>
-  </si>
-  <si>
-    <t>Snakket om quiz på samfunnet</t>
+    <t>Jobbet med skisse påWokwi</t>
   </si>
   <si>
     <t>Snakket om Quizlaget til Håkon</t>
   </si>
   <si>
-    <t>15:00-15:30</t>
-  </si>
-  <si>
-    <t>7 (25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Ferdig med begrensninger og satt inn bilder</t>
-  </si>
-  <si>
-    <t>Jobbet med skisse påWokwi</t>
-  </si>
-  <si>
-    <t>15:40-16:05</t>
-  </si>
-  <si>
-    <t>8 (25 min) ferdig</t>
-  </si>
-  <si>
-    <t>Ble ferdig med disposisjon</t>
-  </si>
-  <si>
     <t>Lagt inn Wokwi-skisse i dsposisjon og skrevet komponentliste</t>
   </si>
   <si>
     <t>Ferdig</t>
+  </si>
+  <si>
+    <t>1324-13:54</t>
+  </si>
+  <si>
+    <t>1324-1355</t>
+  </si>
+  <si>
+    <t>1(25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ble enige og program flow</t>
+  </si>
+  <si>
+    <t>Jobbet med flowchart</t>
+  </si>
+  <si>
+    <t>Spilte på mobil</t>
+  </si>
+  <si>
+    <t>Koste med Ariel  (Hund)</t>
+  </si>
+  <si>
+    <t>13:55-14:20</t>
+  </si>
+  <si>
+    <t>13:55-1420</t>
+  </si>
+  <si>
+    <t>2(25 min) ferdig</t>
+  </si>
+  <si>
+    <t>2 (25 min) ferdig</t>
+  </si>
+  <si>
+    <t>Jobber med program flow.</t>
   </si>
 </sst>
 </file>
@@ -573,17 +609,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="23.88671875" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
     <col min="8" max="8" width="42.33203125" customWidth="1"/>
-    <col min="9" max="9" width="25.77734375" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -610,13 +646,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -624,10 +660,10 @@
         <v>45882</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -653,7 +689,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -668,18 +704,18 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -694,18 +730,18 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -720,18 +756,18 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -746,18 +782,18 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -772,18 +808,18 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -798,18 +834,18 @@
         <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -824,7 +860,59 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45883</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -834,16 +922,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" customWidth="1"/>
     <col min="8" max="8" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -870,13 +958,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -884,10 +972,10 @@
         <v>45882</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -902,10 +990,10 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -913,7 +1001,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -928,18 +1016,18 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -954,18 +1042,18 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -980,18 +1068,18 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -1006,18 +1094,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1032,18 +1120,18 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1058,18 +1146,18 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1087,6 +1175,61 @@
         <v>50</v>
       </c>
       <c r="I9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45883</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8CA1487-953B-461D-8CAA-82A04A7FA363}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97DD1B01-CC80-4AFD-80CD-85043868A596}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="18240" windowHeight="9156" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="115">
   <si>
     <t>Dato</t>
   </si>
@@ -219,9 +219,6 @@
     <t>13:55-14:20</t>
   </si>
   <si>
-    <t>13:55-1420</t>
-  </si>
-  <si>
     <t>2(25 min) ferdig</t>
   </si>
   <si>
@@ -229,19 +226,181 @@
   </si>
   <si>
     <t>Jobber med program flow.</t>
+  </si>
+  <si>
+    <t>1 (25 min+5 min)</t>
+  </si>
+  <si>
+    <t>13:50-14:22</t>
+  </si>
+  <si>
+    <t>Jobber med design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:50-14:22 </t>
+  </si>
+  <si>
+    <t>Snakket med Håkon</t>
+  </si>
+  <si>
+    <t>14:25-14:50</t>
+  </si>
+  <si>
+    <t>14:50-15:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med design, bunnplate </t>
+  </si>
+  <si>
+    <t>15:20-15:46</t>
+  </si>
+  <si>
+    <t>4(25 min)ferdig</t>
+  </si>
+  <si>
+    <t>15:20-1545</t>
+  </si>
+  <si>
+    <t>4 (25 ferdig)</t>
+  </si>
+  <si>
+    <t>Sendte bunnplate til print</t>
+  </si>
+  <si>
+    <t>Sendte nye bunnplate til print</t>
+  </si>
+  <si>
+    <t>13:30-1400</t>
+  </si>
+  <si>
+    <t>Jobber med rapport mens bunnplate prints</t>
+  </si>
+  <si>
+    <t>1435-1500</t>
+  </si>
+  <si>
+    <t>14:50-15:20</t>
+  </si>
+  <si>
+    <t>Hentet vann</t>
+  </si>
+  <si>
+    <t>15:00-1550</t>
+  </si>
+  <si>
+    <t>4 ( 25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Venter på bunnplate. Jobber med rapport</t>
+  </si>
+  <si>
+    <t>2(25min+5min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begynt å koble sammen tenkte krets </t>
+  </si>
+  <si>
+    <t>koblet ferdig og testet krets</t>
+  </si>
+  <si>
+    <t>15:20- 15:50</t>
+  </si>
+  <si>
+    <t>15:50-1620</t>
+  </si>
+  <si>
+    <t>3(25min +5min)</t>
+  </si>
+  <si>
+    <t>Begynt å se på LCD-skjerm</t>
+  </si>
+  <si>
+    <t>5 (25 min) Ferdig</t>
+  </si>
+  <si>
+    <t>Bunnplate ferdig</t>
+  </si>
+  <si>
+    <t>16:20-16:50</t>
+  </si>
+  <si>
+    <t>4(25min + 5min)</t>
+  </si>
+  <si>
+    <t>Koblet opp og lastet ned bibliotek til LCD-skjerm</t>
+  </si>
+  <si>
+    <t>Så på TikTok</t>
+  </si>
+  <si>
+    <t>16:50-17:20</t>
+  </si>
+  <si>
+    <t>Begynt på koden</t>
+  </si>
+  <si>
+    <t>5(25min + 5min)</t>
+  </si>
+  <si>
+    <t>17:20-17:50</t>
+  </si>
+  <si>
+    <t>Forts. kode</t>
+  </si>
+  <si>
+    <t>6(25min+5min)</t>
+  </si>
+  <si>
+    <t>17:50-18:20</t>
+  </si>
+  <si>
+    <t>7(15min)ferdig</t>
+  </si>
+  <si>
+    <t>Ferdig med timer-del av Pomodoro</t>
+  </si>
+  <si>
+    <t>10:15-10:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begynte på top-plate </t>
+  </si>
+  <si>
+    <t>Top-plate ferdig til print</t>
+  </si>
+  <si>
+    <t>Scrollet på telefonen</t>
+  </si>
+  <si>
+    <t>10:50-11:25</t>
+  </si>
+  <si>
+    <t>Startet med teori og nøkkelkonsepter</t>
+  </si>
+  <si>
+    <t>Går til Gras-kurs del 1</t>
+  </si>
+  <si>
+    <t>3 (25 min ) ferdig</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -264,13 +423,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -897,7 +1057,7 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -912,7 +1072,304 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45887</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
         <v>63</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45888</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>1600</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45889</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -931,7 +1388,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" customWidth="1"/>
     <col min="8" max="8" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1209,10 +1666,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
         <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1230,6 +1687,298 @@
         <v>56</v>
       </c>
       <c r="I11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45887</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45888</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97DD1B01-CC80-4AFD-80CD-85043868A596}"/>
+  <xr:revisionPtr revIDLastSave="755" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93DBB6FF-9245-415C-B051-B2EA85EF3BEC}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="18240" windowHeight="9156" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" firstSheet="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="165">
   <si>
     <t>Dato</t>
   </si>
@@ -156,6 +156,102 @@
     <t>Ble ferdig med disposisjon</t>
   </si>
   <si>
+    <t>1324-1355</t>
+  </si>
+  <si>
+    <t>Ble enige og program flow</t>
+  </si>
+  <si>
+    <t>Koste med Ariel  (Hund)</t>
+  </si>
+  <si>
+    <t>13:55-14:20</t>
+  </si>
+  <si>
+    <t>2 (25 min) ferdig</t>
+  </si>
+  <si>
+    <t>Jobber med program flow.</t>
+  </si>
+  <si>
+    <t>13:50-14:22</t>
+  </si>
+  <si>
+    <t>1 (25 min+5 min)</t>
+  </si>
+  <si>
+    <t>Jobber med design</t>
+  </si>
+  <si>
+    <t>14:25-14:50</t>
+  </si>
+  <si>
+    <t>14:50-15:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med design, bunnplate </t>
+  </si>
+  <si>
+    <t>15:20-1545</t>
+  </si>
+  <si>
+    <t>4 (25 ferdig)</t>
+  </si>
+  <si>
+    <t>Sendte bunnplate til print</t>
+  </si>
+  <si>
+    <t>13:30-1400</t>
+  </si>
+  <si>
+    <t>Sendte nye bunnplate til print</t>
+  </si>
+  <si>
+    <t>Jobber med rapport mens bunnplate prints</t>
+  </si>
+  <si>
+    <t>1435-1500</t>
+  </si>
+  <si>
+    <t>Venter på bunnplate. Jobber med rapport</t>
+  </si>
+  <si>
+    <t>15:00-1550</t>
+  </si>
+  <si>
+    <t>4 ( 25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>5 (25 min) Ferdig</t>
+  </si>
+  <si>
+    <t>Bunnplate ferdig</t>
+  </si>
+  <si>
+    <t>10:15-10:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begynte på top-plate </t>
+  </si>
+  <si>
+    <t>10:50-11:25</t>
+  </si>
+  <si>
+    <t>Top-plate ferdig til print</t>
+  </si>
+  <si>
+    <t>Scrollet på telefonen</t>
+  </si>
+  <si>
+    <t>3 (25 min ) ferdig</t>
+  </si>
+  <si>
+    <t>Startet med teori og nøkkelkonsepter</t>
+  </si>
+  <si>
+    <t>Går til Gras-kurs del 1</t>
+  </si>
+  <si>
     <t>Skrev om mål/delmål</t>
   </si>
   <si>
@@ -198,114 +294,48 @@
     <t>1324-13:54</t>
   </si>
   <si>
-    <t>1324-1355</t>
-  </si>
-  <si>
     <t>1(25 min + 5 min)</t>
   </si>
   <si>
-    <t>Ble enige og program flow</t>
-  </si>
-  <si>
     <t>Jobbet med flowchart</t>
   </si>
   <si>
     <t>Spilte på mobil</t>
   </si>
   <si>
-    <t>Koste med Ariel  (Hund)</t>
-  </si>
-  <si>
-    <t>13:55-14:20</t>
-  </si>
-  <si>
     <t>2(25 min) ferdig</t>
   </si>
   <si>
-    <t>2 (25 min) ferdig</t>
-  </si>
-  <si>
-    <t>Jobber med program flow.</t>
-  </si>
-  <si>
-    <t>1 (25 min+5 min)</t>
-  </si>
-  <si>
-    <t>13:50-14:22</t>
-  </si>
-  <si>
-    <t>Jobber med design</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:50-14:22 </t>
   </si>
   <si>
     <t>Snakket med Håkon</t>
   </si>
   <si>
-    <t>14:25-14:50</t>
-  </si>
-  <si>
-    <t>14:50-15:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobber med design, bunnplate </t>
-  </si>
-  <si>
     <t>15:20-15:46</t>
   </si>
   <si>
     <t>4(25 min)ferdig</t>
   </si>
   <si>
-    <t>15:20-1545</t>
-  </si>
-  <si>
-    <t>4 (25 ferdig)</t>
-  </si>
-  <si>
-    <t>Sendte bunnplate til print</t>
-  </si>
-  <si>
-    <t>Sendte nye bunnplate til print</t>
-  </si>
-  <si>
-    <t>13:30-1400</t>
-  </si>
-  <si>
-    <t>Jobber med rapport mens bunnplate prints</t>
-  </si>
-  <si>
-    <t>1435-1500</t>
-  </si>
-  <si>
     <t>14:50-15:20</t>
   </si>
   <si>
+    <t xml:space="preserve">Begynt å koble sammen tenkte krets </t>
+  </si>
+  <si>
     <t>Hentet vann</t>
   </si>
   <si>
-    <t>15:00-1550</t>
-  </si>
-  <si>
-    <t>4 ( 25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Venter på bunnplate. Jobber med rapport</t>
+    <t>15:20- 15:50</t>
   </si>
   <si>
     <t>2(25min+5min)</t>
   </si>
   <si>
-    <t xml:space="preserve">Begynt å koble sammen tenkte krets </t>
-  </si>
-  <si>
     <t>koblet ferdig og testet krets</t>
   </si>
   <si>
-    <t>15:20- 15:50</t>
-  </si>
-  <si>
     <t>15:50-1620</t>
   </si>
   <si>
@@ -315,10 +345,7 @@
     <t>Begynt å se på LCD-skjerm</t>
   </si>
   <si>
-    <t>5 (25 min) Ferdig</t>
-  </si>
-  <si>
-    <t>Bunnplate ferdig</t>
+    <t>Så på TikTok</t>
   </si>
   <si>
     <t>16:20-16:50</t>
@@ -330,27 +357,24 @@
     <t>Koblet opp og lastet ned bibliotek til LCD-skjerm</t>
   </si>
   <si>
-    <t>Så på TikTok</t>
-  </si>
-  <si>
     <t>16:50-17:20</t>
   </si>
   <si>
+    <t>5(25min + 5min)</t>
+  </si>
+  <si>
     <t>Begynt på koden</t>
   </si>
   <si>
-    <t>5(25min + 5min)</t>
-  </si>
-  <si>
     <t>17:20-17:50</t>
   </si>
   <si>
+    <t>6(25min+5min)</t>
+  </si>
+  <si>
     <t>Forts. kode</t>
   </si>
   <si>
-    <t>6(25min+5min)</t>
-  </si>
-  <si>
     <t>17:50-18:20</t>
   </si>
   <si>
@@ -360,28 +384,154 @@
     <t>Ferdig med timer-del av Pomodoro</t>
   </si>
   <si>
-    <t>10:15-10:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Begynte på top-plate </t>
-  </si>
-  <si>
-    <t>Top-plate ferdig til print</t>
-  </si>
-  <si>
-    <t>Scrollet på telefonen</t>
-  </si>
-  <si>
-    <t>10:50-11:25</t>
-  </si>
-  <si>
-    <t>Startet med teori og nøkkelkonsepter</t>
-  </si>
-  <si>
-    <t>Går til Gras-kurs del 1</t>
-  </si>
-  <si>
-    <t>3 (25 min ) ferdig</t>
+    <t>13:50-14:20</t>
+  </si>
+  <si>
+    <t>Finpuss og test av timer</t>
+  </si>
+  <si>
+    <t>Hente vann</t>
+  </si>
+  <si>
+    <t>14:20-14:50</t>
+  </si>
+  <si>
+    <t>Begynt på meny</t>
+  </si>
+  <si>
+    <t>Satt på telefon</t>
+  </si>
+  <si>
+    <t>Forts. meny</t>
+  </si>
+  <si>
+    <t>15:20-15:50</t>
+  </si>
+  <si>
+    <t>15:20-16:10</t>
+  </si>
+  <si>
+    <t>16:10-16:40</t>
+  </si>
+  <si>
+    <t>16:40-17:05</t>
+  </si>
+  <si>
+    <t>7(25min)ferdig</t>
+  </si>
+  <si>
+    <t>18:00-18:30</t>
+  </si>
+  <si>
+    <t>1(25min+5min)</t>
+  </si>
+  <si>
+    <t>18:30-19:00</t>
+  </si>
+  <si>
+    <t>2(25min)ferdig</t>
+  </si>
+  <si>
+    <t>Ferdig med meny - presets</t>
+  </si>
+  <si>
+    <t>08:30-09:00</t>
+  </si>
+  <si>
+    <t>Sett gjennom endringer gjort av Håkon på førsteutkast</t>
+  </si>
+  <si>
+    <t>09:00-09:30</t>
+  </si>
+  <si>
+    <t>Begynt åj obbe på kovertering til minutter</t>
+  </si>
+  <si>
+    <t>09:30-09.55</t>
+  </si>
+  <si>
+    <t>3(25min)ferdig</t>
+  </si>
+  <si>
+    <t>Møtte uforventede komplikasjoner å måtte redde koden</t>
+  </si>
+  <si>
+    <t>ferdig</t>
+  </si>
+  <si>
+    <t>11:25-11:50</t>
+  </si>
+  <si>
+    <t>11:22-11:52</t>
+  </si>
+  <si>
+    <t>Startet med sentral fagteori</t>
+  </si>
+  <si>
+    <t>Ferdig med flowchart</t>
+  </si>
+  <si>
+    <t>11:52-12:22</t>
+  </si>
+  <si>
+    <t>Begynner med måleprinsipper</t>
+  </si>
+  <si>
+    <t>Strakk litt på beina</t>
+  </si>
+  <si>
+    <t>Begynt på Designbeskrivelse</t>
+  </si>
+  <si>
+    <t>12:23-12:54</t>
+  </si>
+  <si>
+    <t>Jobber med måleprinsipper</t>
+  </si>
+  <si>
+    <t>12:55-13:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strakk litt på beina og drakk kaffe </t>
+  </si>
+  <si>
+    <t>13:35-14:05</t>
+  </si>
+  <si>
+    <t>Straks ferdig med måleprinsipper. Begynner snart på state of the art løsning</t>
+  </si>
+  <si>
+    <t>gikk på do</t>
+  </si>
+  <si>
+    <t>Jobber med designbeskrivelse</t>
+  </si>
+  <si>
+    <t>14:05-14:37</t>
+  </si>
+  <si>
+    <t>Har begynt på state of the art delen i rapporten</t>
+  </si>
+  <si>
+    <t>Strakk på beina</t>
+  </si>
+  <si>
+    <t>14:37-15:08</t>
+  </si>
+  <si>
+    <t>Ferdig med første utkast. Skal lese over</t>
+  </si>
+  <si>
+    <t>Gikk på do.</t>
+  </si>
+  <si>
+    <t>15:09-15:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (35 min) ferdig </t>
+  </si>
+  <si>
+    <t>Ferdig med første utkast og klar til levering</t>
   </si>
 </sst>
 </file>
@@ -769,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1028,7 +1178,7 @@
         <v>45883</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -1046,18 +1196,18 @@
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1072,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1080,10 +1230,10 @@
         <v>45887</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1098,7 +1248,7 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1106,7 +1256,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1124,12 +1274,12 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1147,15 +1297,15 @@
         <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1170,7 +1320,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1178,7 +1328,7 @@
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1196,7 +1346,7 @@
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1219,12 +1369,12 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1242,15 +1392,15 @@
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1265,7 +1415,7 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1273,7 +1423,7 @@
         <v>1600</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -1288,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1296,7 +1446,7 @@
         <v>45889</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1314,7 +1464,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1322,7 +1472,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -1340,18 +1490,18 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="2">
-        <v>0.47569444444444442</v>
+      <c r="B23" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -1366,10 +1516,218 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="I23" t="s">
-        <v>113</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>157</v>
+      </c>
+      <c r="I29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30" t="s">
+        <v>160</v>
+      </c>
+      <c r="I30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -1447,10 +1805,10 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1473,18 +1831,18 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1499,10 +1857,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1525,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1551,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -1577,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1603,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -1629,10 +1987,10 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1640,10 +1998,10 @@
         <v>45883</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1658,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1684,10 +2042,10 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1695,10 +2053,10 @@
         <v>45887</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -1713,15 +2071,15 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1739,15 +2097,15 @@
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1765,18 +2123,18 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1791,10 +2149,10 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1802,7 +2160,7 @@
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1820,18 +2178,18 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1846,18 +2204,18 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -1872,18 +2230,18 @@
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -1898,18 +2256,18 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -1924,18 +2282,18 @@
         <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -1950,18 +2308,18 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -1976,10 +2334,501 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45889</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>121</v>
+      </c>
+      <c r="I28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>121</v>
+      </c>
+      <c r="I29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45889</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>9</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>131</v>
+      </c>
+      <c r="I31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45890</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>135</v>
+      </c>
+      <c r="I33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>9</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>7</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>6</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+      <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>9</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>9</v>
+      </c>
+      <c r="F41">
+        <v>9</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="755" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93DBB6FF-9245-415C-B051-B2EA85EF3BEC}"/>
+  <xr:revisionPtr revIDLastSave="836" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1909CFA2-83D4-487F-AE3B-9577EBDFEBF6}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" firstSheet="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="178">
   <si>
     <t>Dato</t>
   </si>
@@ -243,6 +243,9 @@
     <t>Scrollet på telefonen</t>
   </si>
   <si>
+    <t>11:25-11:50</t>
+  </si>
+  <si>
     <t>3 (25 min ) ferdig</t>
   </si>
   <si>
@@ -252,6 +255,69 @@
     <t>Går til Gras-kurs del 1</t>
   </si>
   <si>
+    <t>11:22-11:52</t>
+  </si>
+  <si>
+    <t>Startet med sentral fagteori</t>
+  </si>
+  <si>
+    <t>11:52-12:22</t>
+  </si>
+  <si>
+    <t>Begynner med måleprinsipper</t>
+  </si>
+  <si>
+    <t>Strakk litt på beina</t>
+  </si>
+  <si>
+    <t>12:23-12:54</t>
+  </si>
+  <si>
+    <t>Jobber med måleprinsipper</t>
+  </si>
+  <si>
+    <t>12:55-13:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strakk litt på beina og drakk kaffe </t>
+  </si>
+  <si>
+    <t>13:35-14:05</t>
+  </si>
+  <si>
+    <t>Straks ferdig med måleprinsipper. Begynner snart på state of the art løsning</t>
+  </si>
+  <si>
+    <t>gikk på do</t>
+  </si>
+  <si>
+    <t>14:05-14:37</t>
+  </si>
+  <si>
+    <t>Har begynt på state of the art delen i rapporten</t>
+  </si>
+  <si>
+    <t>Strakk på beina</t>
+  </si>
+  <si>
+    <t>14:37-15:08</t>
+  </si>
+  <si>
+    <t>Ferdig med første utkast. Skal lese over</t>
+  </si>
+  <si>
+    <t>Gikk på do.</t>
+  </si>
+  <si>
+    <t>15:09-15:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (35 min) ferdig </t>
+  </si>
+  <si>
+    <t>Ferdig med første utkast og klar til levering</t>
+  </si>
+  <si>
     <t>Skrev om mål/delmål</t>
   </si>
   <si>
@@ -459,79 +525,52 @@
     <t>ferdig</t>
   </si>
   <si>
-    <t>11:25-11:50</t>
-  </si>
-  <si>
-    <t>11:22-11:52</t>
-  </si>
-  <si>
-    <t>Startet med sentral fagteori</t>
-  </si>
-  <si>
     <t>Ferdig med flowchart</t>
   </si>
   <si>
-    <t>11:52-12:22</t>
-  </si>
-  <si>
-    <t>Begynner med måleprinsipper</t>
-  </si>
-  <si>
-    <t>Strakk litt på beina</t>
-  </si>
-  <si>
     <t>Begynt på Designbeskrivelse</t>
   </si>
   <si>
-    <t>12:23-12:54</t>
-  </si>
-  <si>
-    <t>Jobber med måleprinsipper</t>
-  </si>
-  <si>
-    <t>12:55-13:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strakk litt på beina og drakk kaffe </t>
-  </si>
-  <si>
-    <t>13:35-14:05</t>
-  </si>
-  <si>
-    <t>Straks ferdig med måleprinsipper. Begynner snart på state of the art løsning</t>
-  </si>
-  <si>
-    <t>gikk på do</t>
-  </si>
-  <si>
     <t>Jobber med designbeskrivelse</t>
   </si>
   <si>
-    <t>14:05-14:37</t>
-  </si>
-  <si>
-    <t>Har begynt på state of the art delen i rapporten</t>
-  </si>
-  <si>
-    <t>Strakk på beina</t>
-  </si>
-  <si>
-    <t>14:37-15:08</t>
-  </si>
-  <si>
-    <t>Ferdig med første utkast. Skal lese over</t>
-  </si>
-  <si>
-    <t>Gikk på do.</t>
-  </si>
-  <si>
-    <t>15:09-15:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (35 min) ferdig </t>
-  </si>
-  <si>
-    <t>Ferdig med første utkast og klar til levering</t>
+    <t>12:50-13:15</t>
+  </si>
+  <si>
+    <t>Gjør bunnplate på nytt</t>
+  </si>
+  <si>
+    <t>Omskrive kode til min og sek</t>
+  </si>
+  <si>
+    <t>13:17-13:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forsetter arbeid på bunnplate </t>
+  </si>
+  <si>
+    <t>13:53-14:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med bunnplate </t>
+  </si>
+  <si>
+    <t>14:25-14:56</t>
+  </si>
+  <si>
+    <t>4 (25 min +5 min)</t>
+  </si>
+  <si>
+    <t>Straks ferdig med perfekt bunnplate</t>
+  </si>
+  <si>
+    <t>14:56-15:36</t>
+  </si>
+  <si>
+    <t>5 (40 min ferdig)</t>
+  </si>
+  <si>
+    <t>Ferdig med bunnplate</t>
   </si>
 </sst>
 </file>
@@ -573,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -581,6 +620,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1498,10 +1538,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -1516,10 +1556,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1527,7 +1567,7 @@
         <v>45891</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -1545,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -1553,7 +1593,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -1571,15 +1611,15 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -1597,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1605,7 +1645,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -1623,15 +1663,15 @@
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
@@ -1649,15 +1689,15 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
@@ -1675,15 +1715,15 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
         <v>34</v>
@@ -1701,18 +1741,18 @@
         <v>3</v>
       </c>
       <c r="H30" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -1727,7 +1767,125 @@
         <v>3</v>
       </c>
       <c r="H31" t="s">
-        <v>164</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>7</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -1805,10 +1963,10 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1831,18 +1989,18 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1857,10 +2015,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1883,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1909,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -1935,10 +2093,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1961,7 +2119,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -1987,10 +2145,10 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1998,10 +2156,10 @@
         <v>45883</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -2016,10 +2174,10 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2027,7 +2185,7 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -2042,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2053,7 +2211,7 @@
         <v>45887</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -2071,10 +2229,10 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2097,10 +2255,10 @@
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2123,18 +2281,18 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -2149,10 +2307,10 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2160,7 +2318,7 @@
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -2178,18 +2336,18 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2204,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -2212,10 +2370,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2230,18 +2388,18 @@
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2256,18 +2414,18 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2282,7 +2440,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -2290,10 +2448,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2308,18 +2466,18 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2334,10 +2492,10 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2345,7 +2503,7 @@
         <v>45889</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -2363,18 +2521,18 @@
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="I23" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -2389,18 +2547,18 @@
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2415,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -2423,10 +2581,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2441,18 +2599,18 @@
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I26" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2467,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -2475,10 +2633,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2493,18 +2651,18 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2519,10 +2677,10 @@
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I29" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -2530,10 +2688,10 @@
         <v>45889</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -2548,18 +2706,18 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I30" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -2574,10 +2732,10 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -2585,10 +2743,10 @@
         <v>45890</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -2603,18 +2761,18 @@
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -2629,18 +2787,18 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -2655,10 +2813,10 @@
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -2666,7 +2824,7 @@
         <v>45891</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -2684,18 +2842,18 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="I35" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -2710,15 +2868,15 @@
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -2736,12 +2894,12 @@
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -2759,12 +2917,12 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
@@ -2782,12 +2940,12 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
         <v>30</v>
@@ -2805,12 +2963,12 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
         <v>34</v>
@@ -2828,7 +2986,134 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>155</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="H43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>9</v>
+      </c>
+      <c r="F44">
+        <v>9</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>9</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="H45" t="s">
+        <v>167</v>
+      </c>
+      <c r="I45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="836" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1909CFA2-83D4-487F-AE3B-9577EBDFEBF6}"/>
+  <xr:revisionPtr revIDLastSave="838" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CB0321E-CF38-4950-862A-E0A57122ED36}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="179">
   <si>
     <t>Dato</t>
   </si>
@@ -571,6 +571,9 @@
   </si>
   <si>
     <t>Ferdig med bunnplate</t>
+  </si>
+  <si>
+    <t>Selvregulert læring i dag</t>
   </si>
 </sst>
 </file>
@@ -959,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1796,7 +1799,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>168</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>170</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>172</v>
       </c>
@@ -1865,7 +1868,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>175</v>
       </c>
@@ -1886,6 +1889,14 @@
       </c>
       <c r="H36" s="5" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45895</v>
+      </c>
+      <c r="I37" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="838" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CB0321E-CF38-4950-862A-E0A57122ED36}"/>
+  <xr:revisionPtr revIDLastSave="913" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F309229-FD88-4306-9493-DDF19FA254E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="199">
   <si>
     <t>Dato</t>
   </si>
@@ -574,6 +574,66 @@
   </si>
   <si>
     <t>Selvregulert læring i dag</t>
+  </si>
+  <si>
+    <t>12:26-12:57</t>
+  </si>
+  <si>
+    <t>Jobber med testplan</t>
+  </si>
+  <si>
+    <t>Snakket med Girlsa</t>
+  </si>
+  <si>
+    <t>12:58-13:28</t>
+  </si>
+  <si>
+    <t>2(25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Ferdig med testplan.</t>
+  </si>
+  <si>
+    <t>Gjorde ferdig krets</t>
+  </si>
+  <si>
+    <t>Finpuss av kode</t>
+  </si>
+  <si>
+    <t>13:29-1410</t>
+  </si>
+  <si>
+    <t>13:29-13:59</t>
+  </si>
+  <si>
+    <t>3 (25 min + 15min)</t>
+  </si>
+  <si>
+    <t>Ferdig med kode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med rapport </t>
+  </si>
+  <si>
+    <t>14:10-14:40</t>
+  </si>
+  <si>
+    <t>4 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Jobber med rapport</t>
+  </si>
+  <si>
+    <t>14:10-14:41</t>
+  </si>
+  <si>
+    <t>Jobber med Firmwarearkitektur</t>
+  </si>
+  <si>
+    <t>14:41-15:17</t>
+  </si>
+  <si>
+    <t>5 (25 min)</t>
   </si>
 </sst>
 </file>
@@ -615,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -623,7 +683,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1887,7 +1946,7 @@
       <c r="G36">
         <v>4</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" t="s">
         <v>177</v>
       </c>
     </row>
@@ -1897,6 +1956,127 @@
       </c>
       <c r="I37" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45896</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>9</v>
+      </c>
+      <c r="F38">
+        <v>9</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>180</v>
+      </c>
+      <c r="I38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>8</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42" t="s">
+        <v>198</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -3127,6 +3307,109 @@
         <v>109</v>
       </c>
     </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45895</v>
+      </c>
+      <c r="I47" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45896</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48">
+        <v>7</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+      <c r="F48">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49">
+        <v>7</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="913" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F309229-FD88-4306-9493-DDF19FA254E4}"/>
+  <xr:revisionPtr revIDLastSave="916" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82016AFB-5100-4D70-91A6-E0F7B1903AD7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="199">
   <si>
     <t>Dato</t>
   </si>
@@ -698,10 +698,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1021,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2077,6 +2073,17 @@
       </c>
       <c r="H42" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45897</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="916" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82016AFB-5100-4D70-91A6-E0F7B1903AD7}"/>
+  <xr:revisionPtr revIDLastSave="929" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2271BB-2F18-4DF8-99A1-A678CD3670CB}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="202">
   <si>
     <t>Dato</t>
   </si>
@@ -634,6 +634,15 @@
   </si>
   <si>
     <t>5 (25 min)</t>
+  </si>
+  <si>
+    <t>12:09-12:41</t>
+  </si>
+  <si>
+    <t>12:41-13:18</t>
+  </si>
+  <si>
+    <t>Jobber med testplan delen</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2079,11 +2088,49 @@
       <c r="A43" s="1">
         <v>45897</v>
       </c>
-      <c r="B43" s="2">
-        <v>0.50624999999999998</v>
+      <c r="B43" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
+      </c>
+      <c r="D43">
+        <v>9</v>
+      </c>
+      <c r="E43">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>9</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44">
+        <v>7</v>
+      </c>
+      <c r="E44">
+        <v>7</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="929" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2271BB-2F18-4DF8-99A1-A678CD3670CB}"/>
+  <xr:revisionPtr revIDLastSave="951" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD562FC2-DB0A-4085-A7BF-84D9EB2AEC5C}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="204">
   <si>
     <t>Dato</t>
   </si>
@@ -318,6 +318,96 @@
     <t>Ferdig med første utkast og klar til levering</t>
   </si>
   <si>
+    <t>12:50-13:15</t>
+  </si>
+  <si>
+    <t>Gjør bunnplate på nytt</t>
+  </si>
+  <si>
+    <t>13:17-13:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forsetter arbeid på bunnplate </t>
+  </si>
+  <si>
+    <t>13:53-14:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med bunnplate </t>
+  </si>
+  <si>
+    <t>14:25-14:56</t>
+  </si>
+  <si>
+    <t>4 (25 min +5 min)</t>
+  </si>
+  <si>
+    <t>Straks ferdig med perfekt bunnplate</t>
+  </si>
+  <si>
+    <t>14:56-15:36</t>
+  </si>
+  <si>
+    <t>5 (40 min ferdig)</t>
+  </si>
+  <si>
+    <t>Ferdig med bunnplate</t>
+  </si>
+  <si>
+    <t>Selvregulert læring i dag</t>
+  </si>
+  <si>
+    <t>12:26-12:57</t>
+  </si>
+  <si>
+    <t>Jobber med testplan</t>
+  </si>
+  <si>
+    <t>Snakket med Girlsa</t>
+  </si>
+  <si>
+    <t>12:58-13:28</t>
+  </si>
+  <si>
+    <t>Ferdig med testplan.</t>
+  </si>
+  <si>
+    <t>13:29-1410</t>
+  </si>
+  <si>
+    <t>3 (25 min + 15min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobber med rapport </t>
+  </si>
+  <si>
+    <t>14:10-14:40</t>
+  </si>
+  <si>
+    <t>4 (25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Jobber med rapport</t>
+  </si>
+  <si>
+    <t>14:41-15:17</t>
+  </si>
+  <si>
+    <t>5 (25 min)</t>
+  </si>
+  <si>
+    <t>12:09-12:41</t>
+  </si>
+  <si>
+    <t>12:41-13:18</t>
+  </si>
+  <si>
+    <t>Jobber med testplan delen</t>
+  </si>
+  <si>
+    <t>13:18-13:50</t>
+  </si>
+  <si>
     <t>Skrev om mål/delmål</t>
   </si>
   <si>
@@ -534,122 +624,38 @@
     <t>Jobber med designbeskrivelse</t>
   </si>
   <si>
-    <t>12:50-13:15</t>
-  </si>
-  <si>
-    <t>Gjør bunnplate på nytt</t>
-  </si>
-  <si>
     <t>Omskrive kode til min og sek</t>
   </si>
   <si>
-    <t>13:17-13:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forsetter arbeid på bunnplate </t>
-  </si>
-  <si>
-    <t>13:53-14:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobber med bunnplate </t>
-  </si>
-  <si>
-    <t>14:25-14:56</t>
-  </si>
-  <si>
-    <t>4 (25 min +5 min)</t>
-  </si>
-  <si>
-    <t>Straks ferdig med perfekt bunnplate</t>
-  </si>
-  <si>
-    <t>14:56-15:36</t>
-  </si>
-  <si>
-    <t>5 (40 min ferdig)</t>
-  </si>
-  <si>
-    <t>Ferdig med bunnplate</t>
-  </si>
-  <si>
-    <t>Selvregulert læring i dag</t>
-  </si>
-  <si>
-    <t>12:26-12:57</t>
-  </si>
-  <si>
-    <t>Jobber med testplan</t>
-  </si>
-  <si>
-    <t>Snakket med Girlsa</t>
-  </si>
-  <si>
-    <t>12:58-13:28</t>
+    <t>Gjorde ferdig krets</t>
   </si>
   <si>
     <t>2(25 min + 5 min)</t>
   </si>
   <si>
-    <t>Ferdig med testplan.</t>
-  </si>
-  <si>
-    <t>Gjorde ferdig krets</t>
-  </si>
-  <si>
     <t>Finpuss av kode</t>
   </si>
   <si>
-    <t>13:29-1410</t>
-  </si>
-  <si>
     <t>13:29-13:59</t>
   </si>
   <si>
-    <t>3 (25 min + 15min)</t>
-  </si>
-  <si>
     <t>Ferdig med kode</t>
   </si>
   <si>
-    <t xml:space="preserve">Jobber med rapport </t>
-  </si>
-  <si>
-    <t>14:10-14:40</t>
-  </si>
-  <si>
-    <t>4 (25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Jobber med rapport</t>
-  </si>
-  <si>
     <t>14:10-14:41</t>
   </si>
   <si>
     <t>Jobber med Firmwarearkitektur</t>
   </si>
   <si>
-    <t>14:41-15:17</t>
-  </si>
-  <si>
-    <t>5 (25 min)</t>
-  </si>
-  <si>
-    <t>12:09-12:41</t>
-  </si>
-  <si>
-    <t>12:41-13:18</t>
-  </si>
-  <si>
-    <t>Jobber med testplan delen</t>
+    <t>Begynt på flowchart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1026,21 +1032,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42.28515625" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1072,7 +1078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>45882</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1153,7 +1159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -1231,7 +1237,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>33</v>
       </c>
@@ -1257,7 +1263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>45883</v>
       </c>
@@ -1309,7 +1315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>45887</v>
       </c>
@@ -1361,7 +1367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1407,7 +1413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
         <v>51</v>
       </c>
@@ -1430,7 +1436,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>45888</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="B17" t="s">
         <v>26</v>
       </c>
@@ -1479,7 +1485,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="B20">
         <v>1600</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>45889</v>
       </c>
@@ -1577,7 +1583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="B22" s="2" t="s">
         <v>65</v>
       </c>
@@ -1603,7 +1609,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
@@ -1629,7 +1635,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>45891</v>
       </c>
@@ -1658,7 +1664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="B25" s="2" t="s">
         <v>74</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="B26" s="2" t="s">
         <v>77</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="B27" s="2" t="s">
         <v>79</v>
       </c>
@@ -1736,7 +1742,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="B28" s="2" t="s">
         <v>81</v>
       </c>
@@ -1762,7 +1768,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="B29" s="2" t="s">
         <v>84</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="B30" s="2" t="s">
         <v>87</v>
       </c>
@@ -1814,7 +1820,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="B31" s="2" t="s">
         <v>90</v>
       </c>
@@ -1837,12 +1843,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>45894</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1860,12 +1866,12 @@
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="B33" s="2" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -1883,12 +1889,12 @@
         <v>3</v>
       </c>
       <c r="H33" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="B34" s="2" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
@@ -1906,15 +1912,15 @@
         <v>4</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="B35" s="2" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -1929,15 +1935,15 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="B36" s="2" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="D36">
         <v>8</v>
@@ -1952,23 +1958,23 @@
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>45895</v>
       </c>
       <c r="I37" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>45896</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
@@ -1986,15 +1992,15 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="I38" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="B39" s="2" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -2012,15 +2018,15 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="B40" s="2" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -2035,15 +2041,15 @@
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="B41" s="2" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -2058,15 +2064,15 @@
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="B42" s="2" t="s">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -2081,15 +2087,15 @@
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>45897</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -2107,12 +2113,12 @@
         <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="B44" s="2" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -2130,7 +2136,27 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>201</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2140,20 +2166,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" customWidth="1"/>
-    <col min="8" max="8" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2185,7 +2211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>45882</v>
       </c>
@@ -2208,13 +2234,13 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -2234,18 +2260,18 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -2260,13 +2286,13 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="I4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -2286,13 +2312,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -2312,13 +2338,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -2338,13 +2364,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>33</v>
       </c>
@@ -2364,13 +2390,13 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -2390,21 +2416,21 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>45883</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -2419,18 +2445,18 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -2445,18 +2471,18 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>45887</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -2474,13 +2500,13 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
@@ -2500,13 +2526,13 @@
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
@@ -2526,18 +2552,18 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -2552,18 +2578,18 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -2581,18 +2607,18 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="I16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="B17" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2607,18 +2633,18 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="B18" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2633,18 +2659,18 @@
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="B19" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2659,18 +2685,18 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2685,18 +2711,18 @@
         <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2711,18 +2737,18 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="I21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="B22" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2737,18 +2763,18 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>45889</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -2766,18 +2792,18 @@
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="I23" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="B24" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -2792,18 +2818,18 @@
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="B25" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2818,18 +2844,18 @@
         <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="B26" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2844,18 +2870,18 @@
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="B27" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2870,18 +2896,18 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="B28" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2896,18 +2922,18 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="B29" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2922,21 +2948,21 @@
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>45889</v>
       </c>
       <c r="B30" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -2951,18 +2977,18 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="B31" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -2977,21 +3003,21 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="I31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>45890</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -3006,18 +3032,18 @@
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I32" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="B33" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -3032,18 +3058,18 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="I33" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="B34" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -3058,13 +3084,13 @@
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="I34" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>45891</v>
       </c>
@@ -3087,18 +3113,18 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="I35" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="B36" t="s">
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -3113,13 +3139,13 @@
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I36" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="B37" s="2" t="s">
         <v>77</v>
       </c>
@@ -3139,10 +3165,10 @@
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="B38" s="2" t="s">
         <v>79</v>
       </c>
@@ -3162,10 +3188,10 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="B39" s="2" t="s">
         <v>81</v>
       </c>
@@ -3185,10 +3211,10 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="B40" s="2" t="s">
         <v>84</v>
       </c>
@@ -3208,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="B41" s="2" t="s">
         <v>87</v>
       </c>
@@ -3231,10 +3257,10 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
@@ -3257,12 +3283,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>45894</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -3280,12 +3306,12 @@
         <v>4</v>
       </c>
       <c r="H43" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="B44" s="2" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -3303,15 +3329,15 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="B45" s="2" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
         <v>19</v>
@@ -3329,18 +3355,18 @@
         <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I45" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="B46" s="2" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>8</v>
@@ -3355,26 +3381,26 @@
         <v>4</v>
       </c>
       <c r="H46" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I46" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45895</v>
       </c>
       <c r="I47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>45896</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
@@ -3392,15 +3418,15 @@
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="B49" s="2" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -3415,15 +3441,15 @@
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="B50" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D50">
         <v>8</v>
@@ -3438,15 +3464,15 @@
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="B51" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="D51">
         <v>8</v>
@@ -3461,7 +3487,76 @@
         <v>4</v>
       </c>
       <c r="H51" t="s">
-        <v>196</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>45897</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52">
+        <v>9</v>
+      </c>
+      <c r="E52">
+        <v>9</v>
+      </c>
+      <c r="F52">
+        <v>9</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="B53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53">
+        <v>7</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="B54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="951" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD562FC2-DB0A-4085-A7BF-84D9EB2AEC5C}"/>
+  <xr:revisionPtr revIDLastSave="954" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBAD924D-698D-47B0-91D8-8B36E444370E}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="205">
   <si>
     <t>Dato</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>Begynt på flowchart</t>
+  </si>
+  <si>
+    <t>13:50-15:33</t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2169,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
@@ -3421,7 +3424,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9">
       <c r="B49" s="2" t="s">
         <v>109</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9">
       <c r="B50" t="s">
         <v>199</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9">
       <c r="B51" s="2" t="s">
         <v>201</v>
       </c>
@@ -3490,7 +3493,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>45897</v>
       </c>
@@ -3516,7 +3519,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9">
       <c r="B53" s="2" t="s">
         <v>120</v>
       </c>
@@ -3539,7 +3542,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9">
       <c r="B54" s="2" t="s">
         <v>122</v>
       </c>
@@ -3557,6 +3560,14 @@
       </c>
       <c r="G54">
         <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="B55" t="s">
+        <v>204</v>
+      </c>
+      <c r="I55" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeidslogg/Pomodoro-arkiv.xlsx
+++ b/Arbeidslogg/Pomodoro-arkiv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/hakon_bekken_nmbu_no/Documents/TEL100/Arbeidslogg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="954" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBAD924D-698D-47B0-91D8-8B36E444370E}"/>
+  <xr:revisionPtr revIDLastSave="1166" documentId="8_{11BB530C-2067-4E9D-9BEA-7644CEF8DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41257658-0D5B-4BF8-9740-A15721FA6FC5}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="1" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{7BDAA76B-76AD-4AB8-9BD7-738EACC8EA5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Håkon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="224">
   <si>
     <t>Dato</t>
   </si>
@@ -318,12 +318,231 @@
     <t>Ferdig med første utkast og klar til levering</t>
   </si>
   <si>
+    <t>Skrev om mål/delmål</t>
+  </si>
+  <si>
+    <t>Snakket om fadderuka</t>
+  </si>
+  <si>
+    <t>Så på telefon</t>
+  </si>
+  <si>
+    <t>13:00-13.25</t>
+  </si>
+  <si>
+    <t>3(25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Begynte å se på Wokwi</t>
+  </si>
+  <si>
+    <t>Førte inn dette</t>
+  </si>
+  <si>
+    <t>Hadde problemer med syncing av OneDrive så prøvde å fikse det</t>
+  </si>
+  <si>
+    <t>Gikk på do, og var ute i finværet</t>
+  </si>
+  <si>
+    <t>Jobbet med skisse påWokwi</t>
+  </si>
+  <si>
+    <t>Snakket om Quizlaget til Håkon</t>
+  </si>
+  <si>
+    <t>Lagt inn Wokwi-skisse i dsposisjon og skrevet komponentliste</t>
+  </si>
+  <si>
+    <t>Ferdig</t>
+  </si>
+  <si>
+    <t>1324-13:54</t>
+  </si>
+  <si>
+    <t>1(25 min + 5 min)</t>
+  </si>
+  <si>
+    <t>Jobbet med flowchart</t>
+  </si>
+  <si>
+    <t>Spilte på mobil</t>
+  </si>
+  <si>
+    <t>2(25 min) ferdig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:50-14:22 </t>
+  </si>
+  <si>
+    <t>Snakket med Håkon</t>
+  </si>
+  <si>
+    <t>15:20-15:46</t>
+  </si>
+  <si>
+    <t>4(25 min)ferdig</t>
+  </si>
+  <si>
+    <t>14:50-15:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begynt å koble sammen tenkte krets </t>
+  </si>
+  <si>
+    <t>Hentet vann</t>
+  </si>
+  <si>
+    <t>15:20- 15:50</t>
+  </si>
+  <si>
+    <t>2(25min+5min)</t>
+  </si>
+  <si>
+    <t>koblet ferdig og testet krets</t>
+  </si>
+  <si>
+    <t>15:50-1620</t>
+  </si>
+  <si>
+    <t>3(25min +5min)</t>
+  </si>
+  <si>
+    <t>Begynt å se på LCD-skjerm</t>
+  </si>
+  <si>
+    <t>Så på TikTok</t>
+  </si>
+  <si>
+    <t>16:20-16:50</t>
+  </si>
+  <si>
+    <t>4(25min + 5min)</t>
+  </si>
+  <si>
+    <t>Koblet opp og lastet ned bibliotek til LCD-skjerm</t>
+  </si>
+  <si>
+    <t>16:50-17:20</t>
+  </si>
+  <si>
+    <t>5(25min + 5min)</t>
+  </si>
+  <si>
+    <t>Begynt på koden</t>
+  </si>
+  <si>
+    <t>17:20-17:50</t>
+  </si>
+  <si>
+    <t>6(25min+5min)</t>
+  </si>
+  <si>
+    <t>Forts. kode</t>
+  </si>
+  <si>
+    <t>17:50-18:20</t>
+  </si>
+  <si>
+    <t>7(15min)ferdig</t>
+  </si>
+  <si>
+    <t>Ferdig med timer-del av Pomodoro</t>
+  </si>
+  <si>
+    <t>13:50-14:20</t>
+  </si>
+  <si>
+    <t>Finpuss og test av timer</t>
+  </si>
+  <si>
+    <t>Hente vann</t>
+  </si>
+  <si>
+    <t>14:20-14:50</t>
+  </si>
+  <si>
+    <t>Begynt på meny</t>
+  </si>
+  <si>
+    <t>Satt på telefon</t>
+  </si>
+  <si>
+    <t>Forts. meny</t>
+  </si>
+  <si>
+    <t>15:20-15:50</t>
+  </si>
+  <si>
+    <t>15:20-16:10</t>
+  </si>
+  <si>
+    <t>16:10-16:40</t>
+  </si>
+  <si>
+    <t>16:40-17:05</t>
+  </si>
+  <si>
+    <t>7(25min)ferdig</t>
+  </si>
+  <si>
+    <t>18:00-18:30</t>
+  </si>
+  <si>
+    <t>1(25min+5min)</t>
+  </si>
+  <si>
+    <t>18:30-19:00</t>
+  </si>
+  <si>
+    <t>2(25min)ferdig</t>
+  </si>
+  <si>
+    <t>Ferdig med meny - presets</t>
+  </si>
+  <si>
+    <t>08:30-09:00</t>
+  </si>
+  <si>
+    <t>Sett gjennom endringer gjort av Håkon på førsteutkast</t>
+  </si>
+  <si>
+    <t>09:00-09:30</t>
+  </si>
+  <si>
+    <t>Begynt åj obbe på kovertering til minutter</t>
+  </si>
+  <si>
+    <t>09:30-09.55</t>
+  </si>
+  <si>
+    <t>3(25min)ferdig</t>
+  </si>
+  <si>
+    <t>Møtte uforventede komplikasjoner å måtte redde koden</t>
+  </si>
+  <si>
+    <t>ferdig</t>
+  </si>
+  <si>
+    <t>Ferdig med flowchart</t>
+  </si>
+  <si>
+    <t>Begynt på Designbeskrivelse</t>
+  </si>
+  <si>
+    <t>Jobber med designbeskrivelse</t>
+  </si>
+  <si>
     <t>12:50-13:15</t>
   </si>
   <si>
     <t>Gjør bunnplate på nytt</t>
   </si>
   <si>
+    <t>Omskrive kode til min og sek</t>
+  </si>
+  <si>
     <t>13:17-13:53</t>
   </si>
   <si>
@@ -369,15 +588,30 @@
     <t>12:58-13:28</t>
   </si>
   <si>
+    <t>2(25 min + 5 min)</t>
+  </si>
+  <si>
     <t>Ferdig med testplan.</t>
   </si>
   <si>
+    <t>Gjorde ferdig krets</t>
+  </si>
+  <si>
+    <t>Finpuss av kode</t>
+  </si>
+  <si>
     <t>13:29-1410</t>
   </si>
   <si>
+    <t>13:29-13:59</t>
+  </si>
+  <si>
     <t>3 (25 min + 15min)</t>
   </si>
   <si>
+    <t>Ferdig med kode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jobber med rapport </t>
   </si>
   <si>
@@ -390,6 +624,12 @@
     <t>Jobber med rapport</t>
   </si>
   <si>
+    <t>14:10-14:41</t>
+  </si>
+  <si>
+    <t>Jobber med Firmwarearkitektur</t>
+  </si>
+  <si>
     <t>14:41-15:17</t>
   </si>
   <si>
@@ -408,257 +648,74 @@
     <t>13:18-13:50</t>
   </si>
   <si>
-    <t>Skrev om mål/delmål</t>
-  </si>
-  <si>
-    <t>Snakket om fadderuka</t>
-  </si>
-  <si>
-    <t>Så på telefon</t>
-  </si>
-  <si>
-    <t>13:00-13.25</t>
-  </si>
-  <si>
-    <t>3(25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Begynte å se på Wokwi</t>
-  </si>
-  <si>
-    <t>Førte inn dette</t>
-  </si>
-  <si>
-    <t>Hadde problemer med syncing av OneDrive så prøvde å fikse det</t>
-  </si>
-  <si>
-    <t>Gikk på do, og var ute i finværet</t>
-  </si>
-  <si>
-    <t>Jobbet med skisse påWokwi</t>
-  </si>
-  <si>
-    <t>Snakket om Quizlaget til Håkon</t>
-  </si>
-  <si>
-    <t>Lagt inn Wokwi-skisse i dsposisjon og skrevet komponentliste</t>
-  </si>
-  <si>
-    <t>Ferdig</t>
-  </si>
-  <si>
-    <t>1324-13:54</t>
-  </si>
-  <si>
-    <t>1(25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Jobbet med flowchart</t>
-  </si>
-  <si>
-    <t>Spilte på mobil</t>
-  </si>
-  <si>
-    <t>2(25 min) ferdig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:50-14:22 </t>
-  </si>
-  <si>
-    <t>Snakket med Håkon</t>
-  </si>
-  <si>
-    <t>15:20-15:46</t>
-  </si>
-  <si>
-    <t>4(25 min)ferdig</t>
-  </si>
-  <si>
-    <t>14:50-15:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Begynt å koble sammen tenkte krets </t>
-  </si>
-  <si>
-    <t>Hentet vann</t>
-  </si>
-  <si>
-    <t>15:20- 15:50</t>
-  </si>
-  <si>
-    <t>2(25min+5min)</t>
-  </si>
-  <si>
-    <t>koblet ferdig og testet krets</t>
-  </si>
-  <si>
-    <t>15:50-1620</t>
-  </si>
-  <si>
-    <t>3(25min +5min)</t>
-  </si>
-  <si>
-    <t>Begynt å se på LCD-skjerm</t>
-  </si>
-  <si>
-    <t>Så på TikTok</t>
-  </si>
-  <si>
-    <t>16:20-16:50</t>
-  </si>
-  <si>
-    <t>4(25min + 5min)</t>
-  </si>
-  <si>
-    <t>Koblet opp og lastet ned bibliotek til LCD-skjerm</t>
-  </si>
-  <si>
-    <t>16:50-17:20</t>
-  </si>
-  <si>
-    <t>5(25min + 5min)</t>
-  </si>
-  <si>
-    <t>Begynt på koden</t>
-  </si>
-  <si>
-    <t>17:20-17:50</t>
-  </si>
-  <si>
-    <t>6(25min+5min)</t>
-  </si>
-  <si>
-    <t>Forts. kode</t>
-  </si>
-  <si>
-    <t>17:50-18:20</t>
-  </si>
-  <si>
-    <t>7(15min)ferdig</t>
-  </si>
-  <si>
-    <t>Ferdig med timer-del av Pomodoro</t>
-  </si>
-  <si>
-    <t>13:50-14:20</t>
-  </si>
-  <si>
-    <t>Finpuss og test av timer</t>
-  </si>
-  <si>
-    <t>Hente vann</t>
-  </si>
-  <si>
-    <t>14:20-14:50</t>
-  </si>
-  <si>
-    <t>Begynt på meny</t>
-  </si>
-  <si>
-    <t>Satt på telefon</t>
-  </si>
-  <si>
-    <t>Forts. meny</t>
-  </si>
-  <si>
-    <t>15:20-15:50</t>
-  </si>
-  <si>
-    <t>15:20-16:10</t>
-  </si>
-  <si>
-    <t>16:10-16:40</t>
-  </si>
-  <si>
-    <t>16:40-17:05</t>
-  </si>
-  <si>
-    <t>7(25min)ferdig</t>
-  </si>
-  <si>
-    <t>18:00-18:30</t>
-  </si>
-  <si>
-    <t>1(25min+5min)</t>
-  </si>
-  <si>
-    <t>18:30-19:00</t>
-  </si>
-  <si>
-    <t>2(25min)ferdig</t>
-  </si>
-  <si>
-    <t>Ferdig med meny - presets</t>
-  </si>
-  <si>
-    <t>08:30-09:00</t>
-  </si>
-  <si>
-    <t>Sett gjennom endringer gjort av Håkon på førsteutkast</t>
-  </si>
-  <si>
-    <t>09:00-09:30</t>
-  </si>
-  <si>
-    <t>Begynt åj obbe på kovertering til minutter</t>
-  </si>
-  <si>
-    <t>09:30-09.55</t>
-  </si>
-  <si>
-    <t>3(25min)ferdig</t>
-  </si>
-  <si>
-    <t>Møtte uforventede komplikasjoner å måtte redde koden</t>
-  </si>
-  <si>
-    <t>ferdig</t>
-  </si>
-  <si>
-    <t>Ferdig med flowchart</t>
-  </si>
-  <si>
-    <t>Begynt på Designbeskrivelse</t>
-  </si>
-  <si>
-    <t>Jobber med designbeskrivelse</t>
-  </si>
-  <si>
-    <t>Omskrive kode til min og sek</t>
-  </si>
-  <si>
-    <t>Gjorde ferdig krets</t>
-  </si>
-  <si>
-    <t>2(25 min + 5 min)</t>
-  </si>
-  <si>
-    <t>Finpuss av kode</t>
-  </si>
-  <si>
-    <t>13:29-13:59</t>
-  </si>
-  <si>
-    <t>Ferdig med kode</t>
-  </si>
-  <si>
-    <t>14:10-14:41</t>
-  </si>
-  <si>
-    <t>Jobber med Firmwarearkitektur</t>
-  </si>
-  <si>
     <t>Begynt på flowchart</t>
   </si>
   <si>
     <t>13:50-15:33</t>
+  </si>
+  <si>
+    <t>Selvregulerte pauser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 2 timer </t>
+  </si>
+  <si>
+    <t>12:08-12:38</t>
+  </si>
+  <si>
+    <t>Leser igjennom rapport</t>
+  </si>
+  <si>
+    <t>12:38-13:08</t>
+  </si>
+  <si>
+    <t>Leser igjennom rapport. Finjusterer 3D modell</t>
+  </si>
+  <si>
+    <t>13:08-13:40</t>
+  </si>
+  <si>
+    <t>Finjusterer 3D modell</t>
+  </si>
+  <si>
+    <t>Ferdig med 3D modell</t>
+  </si>
+  <si>
+    <t>5 (25 min +5 min</t>
+  </si>
+  <si>
+    <t>14:15-14:45</t>
+  </si>
+  <si>
+    <t>13:40:14:15</t>
+  </si>
+  <si>
+    <t>Skrive forord</t>
+  </si>
+  <si>
+    <t>14:49-15:16</t>
+  </si>
+  <si>
+    <t>Skriver forord</t>
+  </si>
+  <si>
+    <t>Lenger pause. Spiste kake</t>
+  </si>
+  <si>
+    <t>6 (25 min)</t>
+  </si>
+  <si>
+    <t>vet ikke</t>
+  </si>
+  <si>
+    <t>16:05-16:35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,12 +730,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -693,7 +756,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -701,6 +764,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -716,6 +781,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1035,21 +1104,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BF0A6D-6582-4220-8B8D-0BB20FC0152C}">
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:J64"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="42.28515625" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1081,14 +1150,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45882</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D2">
@@ -1110,11 +1179,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D3">
@@ -1136,11 +1205,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D4">
@@ -1162,11 +1231,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D5">
@@ -1188,11 +1257,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
@@ -1214,11 +1283,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D7">
@@ -1240,11 +1309,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D8">
@@ -1266,11 +1335,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D9">
@@ -1289,14 +1358,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45883</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D10">
@@ -1318,11 +1387,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D11">
@@ -1341,14 +1410,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45887</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D12">
@@ -1370,11 +1439,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D13">
@@ -1393,11 +1462,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D14">
@@ -1416,11 +1485,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D15">
@@ -1439,14 +1508,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D16">
@@ -1465,11 +1534,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D17">
@@ -1488,11 +1557,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D18">
@@ -1511,11 +1580,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D19">
@@ -1534,11 +1603,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1600</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D20">
@@ -1557,14 +1626,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45889</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D21">
@@ -1586,11 +1655,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D22">
@@ -1612,11 +1681,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D23">
@@ -1638,14 +1707,14 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45891</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D24">
@@ -1667,11 +1736,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D25">
@@ -1693,11 +1762,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D26">
@@ -1719,11 +1788,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D27">
@@ -1745,11 +1814,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D28">
@@ -1771,11 +1841,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D29">
@@ -1797,11 +1867,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D30">
@@ -1823,11 +1893,11 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D31">
@@ -1846,14 +1916,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45894</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D32">
@@ -1869,14 +1939,14 @@
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D33">
@@ -1892,14 +1962,14 @@
         <v>3</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D34">
@@ -1915,15 +1985,15 @@
         <v>4</v>
       </c>
       <c r="H34" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
+        <v>172</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -1938,15 +2008,15 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
+        <v>175</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D36">
         <v>8</v>
@@ -1961,25 +2031,28 @@
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45895</v>
       </c>
-      <c r="I37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="C37" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="J37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45896</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D38">
@@ -1995,17 +2068,17 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="I38" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D39">
@@ -2021,15 +2094,15 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>112</v>
+        <v>187</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -2044,15 +2117,15 @@
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" t="s">
-        <v>115</v>
+        <v>192</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -2067,15 +2140,15 @@
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
+        <v>197</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>198</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -2090,17 +2163,17 @@
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45897</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D43">
@@ -2116,14 +2189,14 @@
         <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D44">
@@ -2139,14 +2212,14 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D45">
@@ -2161,6 +2234,192 @@
       <c r="G45">
         <v>3</v>
       </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45899</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48">
+        <v>8</v>
+      </c>
+      <c r="E48">
+        <v>8</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+      <c r="H48" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>8</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52" t="s">
+        <v>219</v>
+      </c>
+      <c r="I52" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C53" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>8</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D64" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2169,20 +2428,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905EF4A-4AD7-426E-AF90-74EE279C8C6D}">
-  <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="8" max="8" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2214,14 +2473,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45882</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D2">
@@ -2237,17 +2496,17 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="I2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D3">
@@ -2263,18 +2522,18 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="I3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
+        <v>96</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -2289,17 +2548,17 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="I4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D5">
@@ -2315,17 +2574,17 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
@@ -2341,17 +2600,17 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D7">
@@ -2367,17 +2626,17 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D8">
@@ -2393,17 +2652,17 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D9">
@@ -2419,21 +2678,21 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="I9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45883</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" t="s">
-        <v>137</v>
+        <v>106</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -2448,18 +2707,18 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
-        <v>140</v>
+      <c r="C11" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -2474,20 +2733,20 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45887</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D12">
@@ -2503,17 +2762,17 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D13">
@@ -2529,17 +2788,17 @@
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D14">
@@ -2555,18 +2814,18 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" t="s">
-        <v>144</v>
+        <v>113</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -2581,20 +2840,20 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45888</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D16">
@@ -2610,18 +2869,18 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="I16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>148</v>
-      </c>
-      <c r="C17" t="s">
-        <v>149</v>
+        <v>118</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2636,18 +2895,18 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C18" t="s">
-        <v>152</v>
+        <v>121</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2662,18 +2921,18 @@
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="I18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C19" t="s">
-        <v>156</v>
+        <v>125</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2688,18 +2947,18 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>158</v>
-      </c>
-      <c r="C20" t="s">
-        <v>159</v>
+        <v>128</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2714,18 +2973,18 @@
         <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" t="s">
-        <v>162</v>
+        <v>131</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2740,18 +2999,18 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" t="s">
-        <v>165</v>
+        <v>134</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2766,20 +3025,20 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45889</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D23">
@@ -2795,18 +3054,18 @@
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="I23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -2821,18 +3080,18 @@
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" t="s">
-        <v>152</v>
+        <v>115</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2847,18 +3106,18 @@
         <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" t="s">
-        <v>156</v>
+        <v>144</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2873,18 +3132,18 @@
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" t="s">
-        <v>159</v>
+        <v>145</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2899,18 +3158,18 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" t="s">
-        <v>162</v>
+        <v>146</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2925,18 +3184,18 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C29" t="s">
-        <v>178</v>
+        <v>147</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2951,21 +3210,21 @@
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45889</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" t="s">
-        <v>180</v>
+        <v>149</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -2980,18 +3239,18 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>181</v>
-      </c>
-      <c r="C31" t="s">
-        <v>182</v>
+        <v>151</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3006,21 +3265,21 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45890</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" t="s">
-        <v>180</v>
+        <v>154</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -3035,18 +3294,18 @@
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" t="s">
-        <v>149</v>
+        <v>156</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -3061,18 +3320,18 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>188</v>
-      </c>
-      <c r="C34" t="s">
-        <v>189</v>
+        <v>158</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -3087,20 +3346,20 @@
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45891</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D35">
@@ -3116,18 +3375,18 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>74</v>
       </c>
-      <c r="C36" t="s">
-        <v>149</v>
+      <c r="C36" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -3142,17 +3401,17 @@
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="I36" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D37">
@@ -3168,14 +3427,14 @@
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D38">
@@ -3191,14 +3450,14 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D39">
@@ -3214,14 +3473,14 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D40">
@@ -3237,14 +3496,14 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D41">
@@ -3260,14 +3519,14 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D42">
@@ -3286,14 +3545,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45894</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D43">
@@ -3309,14 +3568,14 @@
         <v>4</v>
       </c>
       <c r="H43" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D44">
@@ -3332,17 +3591,17 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="I44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D45">
@@ -3358,18 +3617,18 @@
         <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="I45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" t="s">
-        <v>100</v>
+        <v>172</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D46">
         <v>8</v>
@@ -3384,28 +3643,29 @@
         <v>4</v>
       </c>
       <c r="H46" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="I46" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45895</v>
       </c>
+      <c r="C47" s="6"/>
       <c r="I47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45896</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D48">
@@ -3421,15 +3681,15 @@
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>197</v>
+        <v>182</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -3444,15 +3704,15 @@
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>199</v>
-      </c>
-      <c r="C50" t="s">
-        <v>127</v>
+        <v>188</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="D50">
         <v>8</v>
@@ -3467,15 +3727,15 @@
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C51" t="s">
-        <v>156</v>
+        <v>195</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D51">
         <v>8</v>
@@ -3490,17 +3750,17 @@
         <v>4</v>
       </c>
       <c r="H51" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45897</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D52">
@@ -3516,14 +3776,14 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D53">
@@ -3542,11 +3802,11 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C54" t="s">
+        <v>202</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D54">
@@ -3562,12 +3822,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>204</v>
       </c>
       <c r="I55" t="s">
-        <v>105</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>21</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C59" s="5">
+        <v>1.0555555555555556</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D61" s="5">
+        <v>1.3263888888888888</v>
       </c>
     </row>
   </sheetData>
